--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ХРАНИНВЕСТ ЕООД % ДОСТАВКИ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -70,6 +73,24 @@
     <t>2026-05-13</t>
   </si>
   <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
     <t>В9752ВР</t>
   </si>
   <si>
@@ -91,19 +112,55 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>12:07</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>08:53</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:13:00</t>
+  </si>
+  <si>
+    <t>12:07:00</t>
+  </si>
+  <si>
+    <t>15:43:00</t>
+  </si>
+  <si>
+    <t>08:31:00</t>
+  </si>
+  <si>
+    <t>08:53:00</t>
+  </si>
+  <si>
+    <t>23:13:00</t>
+  </si>
+  <si>
+    <t>08:20:00</t>
+  </si>
+  <si>
+    <t>17:27:00</t>
+  </si>
+  <si>
+    <t>3231279241 3231279241</t>
+  </si>
+  <si>
+    <t>3231469105 3231469105</t>
+  </si>
+  <si>
+    <t>3231658481 3231658481</t>
+  </si>
+  <si>
+    <t>3231743785 3231743785</t>
+  </si>
+  <si>
+    <t>3231792046 3231792046</t>
+  </si>
+  <si>
+    <t>3232023043 3232023043</t>
+  </si>
+  <si>
+    <t>3232351166 3232351166</t>
+  </si>
+  <si>
+    <t>3232678530 3232678530</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ДОСТАВКИ</t>
@@ -527,24 +584,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -584,283 +643,433 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1147</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>57.09</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>94.77</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>102.76</v>
       </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>174760</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1156</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>45.37</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>75.31</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>81.67</v>
       </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>78645</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>324064</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1156</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>49.79</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4">
         <v>1.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>82.15000000000001</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.79</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>89.12</v>
       </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>35</v>
       </c>
       <c r="M4">
-        <v>79470</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>425470</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1147</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>36.81</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
         <v>1.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>60.74</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.79</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>65.89</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>179466</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>1147</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>61.33</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
         <v>1.65</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>101.19</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.78</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>109.17</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="L6">
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>42.77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>1.64</v>
+      </c>
+      <c r="I7" s="1">
+        <v>70.14</v>
+      </c>
+      <c r="J7">
+        <v>1.75</v>
+      </c>
+      <c r="K7" s="1">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>105209</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="F8">
+        <v>63.55</v>
+      </c>
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="6">
-        <v>250.39</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.6541</v>
-      </c>
-      <c r="E11" s="6">
-        <v>414.16</v>
-      </c>
-      <c r="F11" s="6">
-        <v>448.61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="9">
-        <v>250.39</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>414.16</v>
-      </c>
-      <c r="F12" s="9">
-        <v>448.61</v>
+      <c r="H8">
+        <v>1.63</v>
+      </c>
+      <c r="I8" s="1">
+        <v>103.59</v>
+      </c>
+      <c r="J8">
+        <v>1.72</v>
+      </c>
+      <c r="K8" s="1">
+        <v>109.31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>36.21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>1.61</v>
+      </c>
+      <c r="I9" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="J9">
+        <v>1.69</v>
+      </c>
+      <c r="K9" s="1">
+        <v>61.19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6">
+        <v>392.92</v>
+      </c>
+      <c r="C14" s="6">
+        <v>8</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.6446</v>
+      </c>
+      <c r="E14" s="6">
+        <v>646.1900000000001</v>
+      </c>
+      <c r="F14" s="6">
+        <v>693.96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="9">
+        <v>392.92</v>
+      </c>
+      <c r="C15" s="9">
+        <v>8</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="9">
+        <v>646.1900000000001</v>
+      </c>
+      <c r="F15" s="9">
+        <v>693.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -214,7 +214,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,12 +224,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,17 +273,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -73,13 +82,16 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В3992ВВ</t>
@@ -103,28 +115,61 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-04 18:11:24</t>
-  </si>
-  <si>
-    <t>2026-06-05 07:53:26</t>
-  </si>
-  <si>
-    <t>2026-06-06 08:21:25</t>
-  </si>
-  <si>
-    <t>2026-06-10 11:24:15</t>
-  </si>
-  <si>
-    <t>2026-06-15 00:12:44</t>
-  </si>
-  <si>
-    <t>2026-06-20 08:37:53</t>
-  </si>
-  <si>
-    <t>2026-06-22 06:13:14</t>
-  </si>
-  <si>
-    <t>2026-06-25 16:33:18</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:11:00</t>
+  </si>
+  <si>
+    <t>07:54:00</t>
+  </si>
+  <si>
+    <t>08:21:00</t>
+  </si>
+  <si>
+    <t>11:24:00</t>
+  </si>
+  <si>
+    <t>00:12:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>06:13:00</t>
+  </si>
+  <si>
+    <t>16:33:00</t>
+  </si>
+  <si>
+    <t>08:25:00</t>
+  </si>
+  <si>
+    <t>3232870621 3232870621</t>
+  </si>
+  <si>
+    <t>3232915937 3232915937</t>
+  </si>
+  <si>
+    <t>3232950418 3232950418</t>
+  </si>
+  <si>
+    <t>3233138889 3233138889</t>
+  </si>
+  <si>
+    <t>3233354268 3233354268</t>
+  </si>
+  <si>
+    <t>3233628719 3233628719</t>
+  </si>
+  <si>
+    <t>3233697265 3233697265</t>
+  </si>
+  <si>
+    <t>3233870029 3233870029</t>
+  </si>
+  <si>
+    <t>3233933878 3233933878</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ДОСТАВКИ</t>
@@ -542,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -551,14 +596,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -592,358 +640,483 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>50.87</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2">
         <v>1.58</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>80.37</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>84.44</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2">
+        <v>426650</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>45.18</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3">
         <v>1.58</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>71.38</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>75</v>
       </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>67.29000000000001</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4">
         <v>1.57</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>105.65</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.64</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>110.36</v>
       </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>39.08</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5">
         <v>1.55</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>60.57</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.63</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>63.7</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
       <c r="F6">
         <v>38.47</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6">
         <v>1.55</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>59.63</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.6</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>61.55</v>
       </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>41.84</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7">
         <v>1.5</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>62.76</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.54</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>64.43000000000001</v>
       </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>64.06999999999999</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8">
         <v>1.47</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>94.18000000000001</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>97.39</v>
       </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>49.94</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9">
         <v>1.46</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>72.91</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.51</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>75.41</v>
       </c>
-      <c r="K9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="L9" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="M9">
+        <v>427300</v>
+      </c>
+      <c r="N9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10">
+        <v>47.06</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10">
+        <v>1.44</v>
+      </c>
+      <c r="I10" s="1">
+        <v>67.77</v>
+      </c>
+      <c r="J10">
+        <v>1.51</v>
+      </c>
+      <c r="K10" s="1">
+        <v>71.06</v>
+      </c>
+      <c r="L10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6">
+        <v>443.8</v>
+      </c>
+      <c r="C15" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="6">
-        <v>396.74</v>
-      </c>
-      <c r="C14" s="6">
-        <v>8</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.5311</v>
-      </c>
-      <c r="E14" s="6">
-        <v>607.45</v>
-      </c>
-      <c r="F14" s="6">
-        <v>632.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="9">
-        <v>396.74</v>
-      </c>
-      <c r="C15" s="9">
-        <v>8</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>607.45</v>
-      </c>
-      <c r="F15" s="9">
-        <v>632.28</v>
+      <c r="D15" s="7">
+        <v>1.5215</v>
+      </c>
+      <c r="E15" s="6">
+        <v>675.22</v>
+      </c>
+      <c r="F15" s="6">
+        <v>703.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="9">
+        <v>443.8</v>
+      </c>
+      <c r="C16" s="9">
+        <v>9</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9">
+        <v>675.22</v>
+      </c>
+      <c r="F16" s="9">
+        <v>703.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -61,28 +67,103 @@
     <t>2026-07-11</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Добрич Добруджа</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>В7860ХА</t>
   </si>
   <si>
+    <t>В3992ВВ</t>
+  </si>
+  <si>
+    <t>В9752ВР</t>
+  </si>
+  <si>
     <t>78970156027720475</t>
   </si>
   <si>
+    <t>78970156027720426</t>
+  </si>
+  <si>
+    <t>78970156027720442</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-02 08:20:34</t>
-  </si>
-  <si>
-    <t>2026-07-07 08:34:39</t>
-  </si>
-  <si>
-    <t>2026-07-11 14:30:21</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:20:00</t>
+  </si>
+  <si>
+    <t>08:34:00</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>08:22:00</t>
+  </si>
+  <si>
+    <t>16:32:00</t>
+  </si>
+  <si>
+    <t>08:42:00</t>
+  </si>
+  <si>
+    <t>18:36:00</t>
+  </si>
+  <si>
+    <t>08:43:00</t>
+  </si>
+  <si>
+    <t>08:32:00</t>
+  </si>
+  <si>
+    <t>3234167799 3234167799</t>
+  </si>
+  <si>
+    <t>3234415488 3234415488</t>
+  </si>
+  <si>
+    <t>3234655654 3234655654</t>
+  </si>
+  <si>
+    <t>3234880850 3234880850</t>
+  </si>
+  <si>
+    <t>3234902986 3234902986</t>
+  </si>
+  <si>
+    <t>3235084868 3235084868</t>
+  </si>
+  <si>
+    <t>3235247412 3235247412</t>
+  </si>
+  <si>
+    <t>3235461263 3235461263</t>
+  </si>
+  <si>
+    <t>3235569026 3235569026</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ДОСТАВКИ</t>
@@ -500,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,15 +590,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,192 +637,480 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>41.33</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>59.1</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>62.41</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>41.98</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>60.45</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>63.81</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>49.69</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
         <v>1.47</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>73.04000000000001</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>76.52</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="L4">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>47.17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>1.53</v>
+      </c>
+      <c r="I5" s="1">
+        <v>72.17</v>
+      </c>
+      <c r="J5">
+        <v>1.61</v>
+      </c>
+      <c r="K5" s="1">
+        <v>75.94</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="N5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>51.96</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>1.53</v>
+      </c>
+      <c r="I6" s="1">
+        <v>79.5</v>
+      </c>
+      <c r="J6">
+        <v>1.61</v>
+      </c>
+      <c r="K6" s="1">
+        <v>83.66</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6">
+        <v>428660</v>
+      </c>
+      <c r="N6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>37.9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>1.58</v>
+      </c>
+      <c r="I7" s="1">
+        <v>59.88</v>
+      </c>
+      <c r="J7">
+        <v>1.68</v>
+      </c>
+      <c r="K7" s="1">
+        <v>63.67</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>34.79</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>1.62</v>
+      </c>
+      <c r="I8" s="1">
+        <v>56.36</v>
+      </c>
+      <c r="J8">
+        <v>1.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>59.14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>66.23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>1.68</v>
+      </c>
+      <c r="I9" s="1">
+        <v>111.27</v>
+      </c>
+      <c r="J9">
+        <v>1.75</v>
+      </c>
+      <c r="K9" s="1">
+        <v>115.9</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>39.62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10">
+        <v>1.7</v>
+      </c>
+      <c r="I10" s="1">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.76</v>
+      </c>
+      <c r="K10" s="1">
+        <v>69.73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="6">
+        <v>410.67</v>
+      </c>
+      <c r="C15" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="6">
-        <v>133</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.448</v>
-      </c>
-      <c r="E9" s="6">
-        <v>192.59</v>
-      </c>
-      <c r="F9" s="6">
-        <v>202.74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9">
-        <v>133</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>192.59</v>
-      </c>
-      <c r="F10" s="9">
-        <v>202.74</v>
+      <c r="D15" s="7">
+        <v>1.5563</v>
+      </c>
+      <c r="E15" s="6">
+        <v>639.12</v>
+      </c>
+      <c r="F15" s="6">
+        <v>670.78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="9">
+        <v>410.67</v>
+      </c>
+      <c r="C16" s="9">
+        <v>9</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9">
+        <v>639.12</v>
+      </c>
+      <c r="F16" s="9">
+        <v>670.78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -190,7 +190,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="7">
-        <v>1.5563</v>
+        <v>1.556286</v>
       </c>
       <c r="E15" s="6">
         <v>639.12</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="57">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -581,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -594,13 +597,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -643,406 +646,436 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>41.33</v>
+        <v>41.331</v>
       </c>
       <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="J2">
+        <v>59.061999</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L2" s="1">
+        <v>62.40981</v>
+      </c>
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
         <v>31</v>
-      </c>
-      <c r="H2">
-        <v>1.43</v>
-      </c>
-      <c r="I2" s="1">
-        <v>59.1</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>62.41</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
       </c>
       <c r="F3">
         <v>41.98</v>
       </c>
       <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>1.406</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.436</v>
+      </c>
+      <c r="J3">
+        <v>60.28328</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L3" s="1">
+        <v>63.8096</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="H3">
-        <v>1.44</v>
-      </c>
-      <c r="I3" s="1">
-        <v>60.45</v>
-      </c>
-      <c r="J3">
-        <v>1.52</v>
-      </c>
-      <c r="K3" s="1">
-        <v>63.81</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3">
+      <c r="F4">
+        <v>49.688</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4">
+        <v>1.437</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.467</v>
+      </c>
+      <c r="J4">
+        <v>72.892296</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L4" s="1">
+        <v>76.51952</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="O4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>47.168</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
+        <v>1.499</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J5">
+        <v>72.119872</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="L5" s="1">
+        <v>75.94047999999999</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>51.963</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>1.499</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J6">
+        <v>79.451427</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="L6" s="1">
+        <v>83.66043000000001</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6">
+        <v>428660</v>
+      </c>
+      <c r="O6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>37.899</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>1.546</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.576</v>
+      </c>
+      <c r="J7">
+        <v>59.728824</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L7" s="1">
+        <v>63.67032</v>
+      </c>
+      <c r="M7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>34.788</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>1.588</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.618</v>
+      </c>
+      <c r="J8">
+        <v>56.286984</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L8" s="1">
+        <v>59.1396</v>
+      </c>
+      <c r="M8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="F4">
-        <v>49.69</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="H4">
-        <v>1.47</v>
-      </c>
-      <c r="I4" s="1">
-        <v>73.04000000000001</v>
-      </c>
-      <c r="J4">
-        <v>1.54</v>
-      </c>
-      <c r="K4" s="1">
-        <v>76.52</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4">
+      <c r="F9">
+        <v>66.229</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>1.653</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.683</v>
+      </c>
+      <c r="J9">
+        <v>111.463407</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L9" s="1">
+        <v>115.90075</v>
+      </c>
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="O9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>47.17</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="H5">
-        <v>1.53</v>
-      </c>
-      <c r="I5" s="1">
-        <v>72.17</v>
-      </c>
-      <c r="J5">
-        <v>1.61</v>
-      </c>
-      <c r="K5" s="1">
-        <v>75.94</v>
-      </c>
-      <c r="L5" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5">
+      <c r="F10">
+        <v>39.619</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>1.674</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J10">
+        <v>67.51077600000001</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L10" s="1">
+        <v>69.72944</v>
+      </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>51.96</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6">
-        <v>1.53</v>
-      </c>
-      <c r="I6" s="1">
-        <v>79.5</v>
-      </c>
-      <c r="J6">
-        <v>1.61</v>
-      </c>
-      <c r="K6" s="1">
-        <v>83.66</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6">
-        <v>428660</v>
-      </c>
-      <c r="N6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>37.9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>1.58</v>
-      </c>
-      <c r="I7" s="1">
-        <v>59.88</v>
-      </c>
-      <c r="J7">
-        <v>1.68</v>
-      </c>
-      <c r="K7" s="1">
-        <v>63.67</v>
-      </c>
-      <c r="L7" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8">
-        <v>34.79</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8">
-        <v>1.62</v>
-      </c>
-      <c r="I8" s="1">
-        <v>56.36</v>
-      </c>
-      <c r="J8">
-        <v>1.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>59.14</v>
-      </c>
-      <c r="L8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>66.23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9">
-        <v>1.68</v>
-      </c>
-      <c r="I9" s="1">
-        <v>111.27</v>
-      </c>
-      <c r="J9">
-        <v>1.75</v>
-      </c>
-      <c r="K9" s="1">
-        <v>115.9</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10">
-        <v>39.62</v>
-      </c>
-      <c r="G10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10">
-        <v>1.7</v>
-      </c>
-      <c r="I10" s="1">
-        <v>67.34999999999999</v>
-      </c>
-      <c r="J10">
-        <v>1.76</v>
-      </c>
-      <c r="K10" s="1">
-        <v>69.73</v>
-      </c>
-      <c r="L10" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1050,59 +1083,59 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="6">
-        <v>410.67</v>
+        <v>410.665</v>
       </c>
       <c r="C15" s="6">
         <v>9</v>
       </c>
       <c r="D15" s="7">
-        <v>1.556286</v>
+        <v>1.555523</v>
       </c>
       <c r="E15" s="6">
-        <v>639.12</v>
+        <v>638.8</v>
       </c>
       <c r="F15" s="6">
         <v>670.78</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="9">
-        <v>410.67</v>
+        <v>410.665</v>
       </c>
       <c r="C16" s="9">
         <v>9</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9">
-        <v>639.12</v>
+        <v>638.8</v>
       </c>
       <c r="F16" s="9">
         <v>670.78</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ/ХРАНИНВЕСТ ЕООД % ДОСТАВКИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -192,8 +189,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -286,10 +283,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -584,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -597,13 +594,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -646,436 +643,406 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>41.331</v>
       </c>
       <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>59.062</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>62.41</v>
+      </c>
+      <c r="L2" t="s">
         <v>32</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.429</v>
-      </c>
-      <c r="J2">
-        <v>59.061999</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>62.40981</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>41.98</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I3" s="1">
-        <v>1.436</v>
+        <v>60.283</v>
       </c>
       <c r="J3">
-        <v>60.28328</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>63.8096</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3">
+        <v>63.81</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>49.688</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I4" s="1">
-        <v>1.467</v>
+        <v>72.892</v>
       </c>
       <c r="J4">
-        <v>72.892296</v>
+        <v>1.54</v>
       </c>
       <c r="K4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L4" s="1">
-        <v>76.51952</v>
-      </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4">
+        <v>76.52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>47.168</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I5" s="1">
-        <v>1.529</v>
+        <v>72.12</v>
       </c>
       <c r="J5">
-        <v>72.119872</v>
+        <v>1.61</v>
       </c>
       <c r="K5" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L5" s="1">
-        <v>75.94047999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5">
+        <v>75.94</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>51.963</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I6" s="1">
-        <v>1.529</v>
+        <v>79.45099999999999</v>
       </c>
       <c r="J6">
-        <v>79.451427</v>
+        <v>1.61</v>
       </c>
       <c r="K6" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L6" s="1">
-        <v>83.66043000000001</v>
-      </c>
-      <c r="M6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6">
+        <v>83.66</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6">
         <v>428660</v>
       </c>
-      <c r="O6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>37.899</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I7" s="1">
-        <v>1.576</v>
+        <v>59.729</v>
       </c>
       <c r="J7">
-        <v>59.728824</v>
+        <v>1.68</v>
       </c>
       <c r="K7" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L7" s="1">
-        <v>63.67032</v>
-      </c>
-      <c r="M7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7">
+        <v>63.67</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>34.788</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I8" s="1">
-        <v>1.618</v>
+        <v>56.287</v>
       </c>
       <c r="J8">
-        <v>56.286984</v>
+        <v>1.7</v>
       </c>
       <c r="K8" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L8" s="1">
-        <v>59.1396</v>
-      </c>
-      <c r="M8" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8">
+        <v>59.14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
       </c>
       <c r="F9">
         <v>66.229</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I9" s="1">
-        <v>1.683</v>
+        <v>111.463</v>
       </c>
       <c r="J9">
-        <v>111.463407</v>
+        <v>1.75</v>
       </c>
       <c r="K9" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L9" s="1">
-        <v>115.90075</v>
-      </c>
-      <c r="M9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9">
+        <v>115.901</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>39.619</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I10" s="1">
-        <v>1.704</v>
+        <v>67.511</v>
       </c>
       <c r="J10">
-        <v>67.51077600000001</v>
+        <v>1.76</v>
       </c>
       <c r="K10" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L10" s="1">
-        <v>69.72944</v>
-      </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10">
+        <v>69.729</v>
+      </c>
+      <c r="L10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1083,49 +1050,49 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="6">
         <v>410.665</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>9</v>
       </c>
       <c r="D15" s="7">
-        <v>1.555523</v>
-      </c>
-      <c r="E15" s="6">
-        <v>638.8</v>
-      </c>
-      <c r="F15" s="6">
+        <v>1.556</v>
+      </c>
+      <c r="E15" s="7">
+        <v>638.798</v>
+      </c>
+      <c r="F15" s="7">
         <v>670.78</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="9">
         <v>410.665</v>
@@ -1135,7 +1102,7 @@
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9">
-        <v>638.8</v>
+        <v>638.798</v>
       </c>
       <c r="F16" s="9">
         <v>670.78</v>
